--- a/faecher/informatik/klasse-9/1-Tabellenkalkulation/4-Einführung-WENN.xlsx
+++ b/faecher/informatik/klasse-9/1-Tabellenkalkulation/4-Einführung-WENN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503D5AC5-22B5-4C0E-A2E1-7607FA803EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B24DA7-EE78-4102-B53D-C19DD41C1640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -64,12 +64,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -84,8 +90,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -415,6 +422,7 @@
       <c r="B5">
         <v>2</v>
       </c>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -423,6 +431,7 @@
       <c r="B6">
         <v>3</v>
       </c>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -431,6 +440,7 @@
       <c r="B7">
         <v>4</v>
       </c>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -439,6 +449,7 @@
       <c r="B8">
         <v>5</v>
       </c>
+      <c r="D8" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
